--- a/categories.xlsx
+++ b/categories.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Order</t>
   </si>
@@ -25,76 +25,28 @@
     <t>Arabic_Category</t>
   </si>
   <si>
-    <t>Soups</t>
-  </si>
-  <si>
-    <t>شوربة</t>
-  </si>
-  <si>
-    <t>Salads</t>
-  </si>
-  <si>
-    <t>سلطات</t>
-  </si>
-  <si>
-    <t>Sandwiches</t>
-  </si>
-  <si>
-    <t>سندوتشات</t>
-  </si>
-  <si>
-    <t>Special Dishes</t>
-  </si>
-  <si>
-    <t>أطباق خاصة</t>
-  </si>
-  <si>
-    <t>Tajiens</t>
-  </si>
-  <si>
-    <t>طواجن</t>
-  </si>
-  <si>
-    <t>Fatta</t>
-  </si>
-  <si>
-    <t>فتة</t>
-  </si>
-  <si>
-    <t>Rice &amp; Pasta</t>
-  </si>
-  <si>
-    <t>أرز ومكرونة</t>
-  </si>
-  <si>
-    <t>Grilled Beef</t>
-  </si>
-  <si>
-    <t>لحم مشوي</t>
-  </si>
-  <si>
-    <t>Grilled Chicken</t>
-  </si>
-  <si>
-    <t>فراخ مشوية</t>
-  </si>
-  <si>
-    <t>Mix Grill</t>
-  </si>
-  <si>
-    <t>مشويات مشكلة</t>
-  </si>
-  <si>
-    <t>Savoury Fateer</t>
-  </si>
-  <si>
-    <t>فطير حادق</t>
-  </si>
-  <si>
-    <t>Sweet Fateer</t>
-  </si>
-  <si>
-    <t>فطير حلو</t>
+    <t>Starters</t>
+  </si>
+  <si>
+    <t>مقبلات</t>
+  </si>
+  <si>
+    <t>Egyptian Dishes</t>
+  </si>
+  <si>
+    <t>الأطباق المصرية</t>
+  </si>
+  <si>
+    <t>Grills &amp; Barbecue</t>
+  </si>
+  <si>
+    <t>المشاوي</t>
+  </si>
+  <si>
+    <t>Fateer</t>
+  </si>
+  <si>
+    <t>الفطير</t>
   </si>
   <si>
     <t>Desserts</t>
@@ -108,10 +60,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -132,9 +84,70 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -147,26 +160,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -174,78 +182,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -260,7 +198,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -275,31 +227,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -311,151 +395,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -466,6 +418,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -508,45 +475,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -566,147 +494,171 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -796,8 +748,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:C14" totalsRowShown="0">
-  <autoFilter ref="A1:C14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:C6" totalsRowShown="0">
+  <autoFilter ref="A1:C6"/>
   <tableColumns count="3">
     <tableColumn id="1" name="Order" dataDxfId="0"/>
     <tableColumn id="2" name="Category"/>
@@ -1065,10 +1017,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="6.75" customWidth="1"/>
+    <col min="1" max="1" width="8.125" customWidth="1"/>
     <col min="2" max="2" width="19.875" customWidth="1"/>
     <col min="3" max="3" width="15.75" customWidth="1"/>
   </cols>
@@ -1106,7 +1058,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" ht="28.5" spans="1:3">
+    <row r="4" spans="1:3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1117,7 +1069,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="28.5" spans="1:3">
+    <row r="5" spans="1:3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1135,96 +1087,8 @@
       <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" ht="28.5" spans="1:3">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" ht="28.5" spans="1:3">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" ht="28.5" spans="1:3">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" ht="28.5" spans="1:3">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" ht="28.5" spans="1:3">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" ht="28.5" spans="1:3">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="1">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
